--- a/Doku/Testplan.xlsx
+++ b/Doku/Testplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonasmuhlbach/Programs_VB/Spiel_1.0/Doku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92D7F824-CC12-8D43-A8C4-DCFB2F507FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57A586D-ED9A-DD4E-8A13-3877018A74A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16120" xr2:uid="{FE7696FD-3E9E-A242-81BB-4231A40AE5FF}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15980" xr2:uid="{FE7696FD-3E9E-A242-81BB-4231A40AE5FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Funktion</t>
   </si>
@@ -54,6 +54,36 @@
   </si>
   <si>
     <t>Kommentar</t>
+  </si>
+  <si>
+    <t>Bewegung des Spielers nach links durch klicken</t>
+  </si>
+  <si>
+    <t>Bewegung des Spielers nach rechts durch klicken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durch langes drücken bewegt sich der Spieler schneller </t>
+  </si>
+  <si>
+    <t>Bei berührung eines Hindernisses wird ein Leben abgezogen</t>
+  </si>
+  <si>
+    <t>Sobald die Leben auf  0 fallen kommt ein Game Over Bildschirm</t>
+  </si>
+  <si>
+    <t>Die Hindernissdichte geht nicht über 5 in einer Reihe</t>
+  </si>
+  <si>
+    <t>ein Hindernissblock ist maximal 9 Zeichen groß</t>
+  </si>
+  <si>
+    <t>Die Leben werden in der unteren Linke Ecke angezeigt</t>
+  </si>
+  <si>
+    <t>Die Geschwindigeit steigert sich im Laufe des Spiels</t>
+  </si>
+  <si>
+    <t>Die Dichte an Hindernissen steigern sich im Laufe des Games</t>
   </si>
 </sst>
 </file>
@@ -456,12 +486,12 @@
   <dimension ref="A1:I1048576"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="1" max="1" width="54.33203125" customWidth="1"/>
     <col min="2" max="2" width="2" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="5" max="5" width="2.1640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.1640625" customWidth="1"/>
+    <col min="6" max="6" width="48.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -495,61 +525,81 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="4"/>
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
+      <c r="A12" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="F12" s="4"/>

--- a/Doku/Testplan.xlsx
+++ b/Doku/Testplan.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Doku/Testplan.xlsx
+++ b/Doku/Testplan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonasmuhlbach/Programs_VB/Spiel_1.0/Doku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57A586D-ED9A-DD4E-8A13-3877018A74A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA353AE-1DE2-4B48-9386-7BFF73934B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15980" xr2:uid="{FE7696FD-3E9E-A242-81BB-4231A40AE5FF}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{FE7696FD-3E9E-A242-81BB-4231A40AE5FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>Funktion</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
   <si>
     <t>Testet</t>
   </si>
@@ -56,15 +53,6 @@
     <t>Kommentar</t>
   </si>
   <si>
-    <t>Bewegung des Spielers nach links durch klicken</t>
-  </si>
-  <si>
-    <t>Bewegung des Spielers nach rechts durch klicken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durch langes drücken bewegt sich der Spieler schneller </t>
-  </si>
-  <si>
     <t>Bei berührung eines Hindernisses wird ein Leben abgezogen</t>
   </si>
   <si>
@@ -84,6 +72,132 @@
   </si>
   <si>
     <t>Die Dichte an Hindernissen steigern sich im Laufe des Games</t>
+  </si>
+  <si>
+    <t>Testfall</t>
+  </si>
+  <si>
+    <t>Nr</t>
+  </si>
+  <si>
+    <t>Thema</t>
+  </si>
+  <si>
+    <t>Testschritt</t>
+  </si>
+  <si>
+    <t>Beschreibung</t>
+  </si>
+  <si>
+    <t>Erwartetes Ergebnis</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Bewegung Spielfigur</t>
+  </si>
+  <si>
+    <t>Cursor-Taste rechts kurz drücken</t>
+  </si>
+  <si>
+    <t>Spielfigur bewegt sich um 1 Spalte nach rechts</t>
+  </si>
+  <si>
+    <t>Cursor-Taste links kurz drücken</t>
+  </si>
+  <si>
+    <t>Spielfigur bewegt sich um 1 Spalte nach links</t>
+  </si>
+  <si>
+    <t>Cursor-Taste rechts ca 1 sekunde lang drücken</t>
+  </si>
+  <si>
+    <t>Spielfigur bewegt sich schnell nach rechts und bleibt beim loslassen der Taste sofort stehen</t>
+  </si>
+  <si>
+    <t>Cursor-Taste links ca 1 sekunde lang drücken</t>
+  </si>
+  <si>
+    <t>Spielfigur bewegt sich schnell nach links und bleibt beim loslassen der Taste sofort stehen</t>
+  </si>
+  <si>
+    <t>Cursor-Taste rechts lange drücken</t>
+  </si>
+  <si>
+    <t>Spielfigur bewegt sich schnell nach rechts und bleibt am Spielrand stehen</t>
+  </si>
+  <si>
+    <t>Cursor-Taste links lange drücken</t>
+  </si>
+  <si>
+    <t>Spielfigur bewegt sich schnell nach links und bleibt am Spielrand stehen</t>
+  </si>
+  <si>
+    <t>Cursor-Taste nicht drücken</t>
+  </si>
+  <si>
+    <t>Spielfigur bewegt sich nicht</t>
+  </si>
+  <si>
+    <t>Hindernisse</t>
+  </si>
+  <si>
+    <t>Spiel starten</t>
+  </si>
+  <si>
+    <t>Hindernisse erscheinen in der obersten Zeile und sind zufällig verteilt</t>
+  </si>
+  <si>
+    <t>Hindernisse bewegen sich zeilenweise nach unten</t>
+  </si>
+  <si>
+    <t>Ein Hinderniss Block besteht immer aus einer Einheit "Auto"</t>
+  </si>
+  <si>
+    <t>Spiel lange laufen lassen</t>
+  </si>
+  <si>
+    <t>Hindernisdichte und Geschwindigkeit nehmen zu</t>
+  </si>
+  <si>
+    <t>Hindenrisse sind mal in allen Spalten</t>
+  </si>
+  <si>
+    <t>Kollisionserkennung</t>
+  </si>
+  <si>
+    <t>Spielfigur unter nahendes Hindernis setzen</t>
+  </si>
+  <si>
+    <t>Abzug eines Lebens</t>
+  </si>
+  <si>
+    <t>Ausgabe eines Warntons</t>
+  </si>
+  <si>
+    <t>Hinderniss wird eine "Auto" Großes Feld gelöscht</t>
+  </si>
+  <si>
+    <t>Kolllision wird erkannt</t>
+  </si>
+  <si>
+    <t>Spielfigur auf Spalte links von nahendem Auto setzen</t>
+  </si>
+  <si>
+    <t>Keine Kollisison</t>
+  </si>
+  <si>
+    <t>Spielfigur auf Spalte rechts von nahendem Auto setzen</t>
+  </si>
+  <si>
+    <t>Spielfigur mehrmals Kollidieren lassen</t>
+  </si>
+  <si>
+    <t>Das Spiel endet, wenn alle Leben verbraucht sind.</t>
+  </si>
+  <si>
+    <t>Anzeige "Game Over"</t>
   </si>
 </sst>
 </file>
@@ -483,267 +597,507 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5974090F-34E1-CE4F-8A3E-CE766C661239}">
-  <dimension ref="A1:I1048576"/>
+  <dimension ref="A1:N1048576"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="54.33203125" customWidth="1"/>
-    <col min="2" max="2" width="2" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="2.1640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="48.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" customWidth="1"/>
+    <col min="4" max="4" width="54.33203125" customWidth="1"/>
+    <col min="5" max="5" width="75.6640625" customWidth="1"/>
+    <col min="6" max="6" width="54.33203125" customWidth="1"/>
+    <col min="7" max="7" width="2" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.5" customWidth="1"/>
+    <col min="10" max="10" width="2.1640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="48.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C5">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="C2" s="1" t="s">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C19">
         <v>2</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="D19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C22">
         <v>5</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="D22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="K22" s="4"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="K24" s="4"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C29">
         <v>6</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="D29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C30">
         <v>7</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="F26" s="4"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="F30" s="4"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="4"/>
-      <c r="C31" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="K30" s="4"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="F31" s="4"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="4"/>
-      <c r="C32" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="4"/>
-      <c r="C33" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="K32" s="4"/>
+    </row>
+    <row r="33" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="4"/>
-      <c r="C34" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="C35" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="K34" s="4"/>
+    </row>
+    <row r="35" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-    </row>
-    <row r="1048576" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1048576" s="3"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="K35" s="4"/>
+    </row>
+    <row r="1048576" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D1048576" s="3"/>
+      <c r="E1048576" s="3"/>
+      <c r="F1048576" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Doku/Testplan.xlsx
+++ b/Doku/Testplan.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonasmuhlbach/Programs_VB/Spiel_1.0/Doku/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA353AE-1DE2-4B48-9386-7BFF73934B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777940A3-2909-C542-8B6F-D5DE7E327085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{FE7696FD-3E9E-A242-81BB-4231A40AE5FF}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="14420" windowHeight="15940" xr2:uid="{FE7696FD-3E9E-A242-81BB-4231A40AE5FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabelle3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="94">
   <si>
     <t>Testet</t>
   </si>
@@ -53,27 +54,6 @@
     <t>Kommentar</t>
   </si>
   <si>
-    <t>Bei berührung eines Hindernisses wird ein Leben abgezogen</t>
-  </si>
-  <si>
-    <t>Sobald die Leben auf  0 fallen kommt ein Game Over Bildschirm</t>
-  </si>
-  <si>
-    <t>Die Hindernissdichte geht nicht über 5 in einer Reihe</t>
-  </si>
-  <si>
-    <t>ein Hindernissblock ist maximal 9 Zeichen groß</t>
-  </si>
-  <si>
-    <t>Die Leben werden in der unteren Linke Ecke angezeigt</t>
-  </si>
-  <si>
-    <t>Die Geschwindigeit steigert sich im Laufe des Spiels</t>
-  </si>
-  <si>
-    <t>Die Dichte an Hindernissen steigern sich im Laufe des Games</t>
-  </si>
-  <si>
     <t>Testfall</t>
   </si>
   <si>
@@ -194,10 +174,154 @@
     <t>Spielfigur mehrmals Kollidieren lassen</t>
   </si>
   <si>
-    <t>Das Spiel endet, wenn alle Leben verbraucht sind.</t>
-  </si>
-  <si>
-    <t>Anzeige "Game Over"</t>
+    <t>Voraussetzungen</t>
+  </si>
+  <si>
+    <t>Im Spielablauf testen</t>
+  </si>
+  <si>
+    <t>Im Spielablauf testen mit Tastatur</t>
+  </si>
+  <si>
+    <t>Im Spielablauf testen ohne Tastatur</t>
+  </si>
+  <si>
+    <t>Startbildschirm</t>
+  </si>
+  <si>
+    <t>Im Startbildschirm testen</t>
+  </si>
+  <si>
+    <t>Roter Blitz</t>
+  </si>
+  <si>
+    <t>Das Spiel endet, wenn alle Leben verbraucht sind. Anzeige "Game Over"</t>
+  </si>
+  <si>
+    <t>Intro wird abgespielt</t>
+  </si>
+  <si>
+    <t>Startbildschirm aufrufen</t>
+  </si>
+  <si>
+    <t>Bildschirm mit Optionen zum Auswählen</t>
+  </si>
+  <si>
+    <t>User kriegt die Auswahl zwischen drei Schwierigkeiten (Leicht,Mittel Schwer)</t>
+  </si>
+  <si>
+    <t>User kriegt die Auswahl zwische verschiedenen Farben und kann die wälen die ihm am besten passt</t>
+  </si>
+  <si>
+    <t>Startbildschirm aufrufen und Auswahl Scoreboard Option</t>
+  </si>
+  <si>
+    <t>User kriegt eine Anzeige der Top Plätze jeder Schwierigkeit</t>
+  </si>
+  <si>
+    <t>Game über die Konsole Starten</t>
+  </si>
+  <si>
+    <t>Startbildschirm aufrufen und Auswahl der Spiel Starten Option</t>
+  </si>
+  <si>
+    <t>Das Spiel wird gesarten und man muss zeigen was man kann</t>
+  </si>
+  <si>
+    <t>Startbildschirm aufrufen und Auswahl der Schwierigkeit Option</t>
+  </si>
+  <si>
+    <t>Startbildschirm aufrufen und Auswahl Auto Optik Option</t>
+  </si>
+  <si>
+    <t>Hindernisse erscheinen in der Mitte Spur je ein Pixel rechts und links zu Spurmarkierungen</t>
+  </si>
+  <si>
+    <t>Spielfeld</t>
+  </si>
+  <si>
+    <t>Es werden 11 Spuren erzeugt</t>
+  </si>
+  <si>
+    <t>Die Spurmarkirungen sind immer gleich 2 Striche einer frei</t>
+  </si>
+  <si>
+    <t>Spiel Starten</t>
+  </si>
+  <si>
+    <t>Spiel starten und Game etwas laufen lassen</t>
+  </si>
+  <si>
+    <t>Der Spieler wird in der Mitte des Spielfeldes gespawnt</t>
+  </si>
+  <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>Ein "B" das auf dem Spielfeld ist berühren</t>
+  </si>
+  <si>
+    <t>Die Steuerung wird umgekehrt</t>
+  </si>
+  <si>
+    <t>Die Spielfeldfarbe ändert sich von Weiß auf Grün</t>
+  </si>
+  <si>
+    <t>Der Efekt hält für 10 Sekunden</t>
+  </si>
+  <si>
+    <t>Es wird unten in der Mitte angezeigt das die Steuerung umgedreht ist</t>
+  </si>
+  <si>
+    <t>Ein"*" das auf dem Spielfeld ist berühren</t>
+  </si>
+  <si>
+    <t>Die Hiterkennung wird ausgeschaltet und man veliert kein leben mehr</t>
+  </si>
+  <si>
+    <t>"Die Spielfarbe ändert sich von Weiß auf Gelb"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Efekt hält für 10 Sekunden </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es wird unten in der Mitte angezeigt das man unverwundbar ist </t>
+  </si>
+  <si>
+    <t>Ein "S" das auf dem Spielfeld ist berühren</t>
+  </si>
+  <si>
+    <t>Ein"+" das auf dem Spielfeld ist berühren</t>
+  </si>
+  <si>
+    <t>Der Spieler erhält ein extra leben</t>
+  </si>
+  <si>
+    <t>Unter ganz links werden die verbleibenden Leben angezeigt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neben den leben werden die aktuellen Punkte angezeigt </t>
+  </si>
+  <si>
+    <t>Punkte Starten bei 0</t>
+  </si>
+  <si>
+    <t>Neben den Punkten wird der aktuelle Efekt angezeigt</t>
+  </si>
+  <si>
+    <t>Spiel starten und Game etwas laufen lassen und ein Bustabe Aufsameln</t>
+  </si>
+  <si>
+    <t>Game Over Bildschirm</t>
+  </si>
+  <si>
+    <t>Alle Leben verlieren</t>
+  </si>
+  <si>
+    <t>Name des Spielers eintragen im Feld</t>
+  </si>
+  <si>
+    <t>Name mit Score taucht in der Bestenliste auf (nur wenn Gut genug ;))</t>
   </si>
 </sst>
 </file>
@@ -257,12 +381,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -597,509 +727,871 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5974090F-34E1-CE4F-8A3E-CE766C661239}">
-  <dimension ref="A1:N1048576"/>
+  <dimension ref="A1:O1048557"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
-    <col min="4" max="4" width="54.33203125" customWidth="1"/>
-    <col min="5" max="5" width="75.6640625" customWidth="1"/>
-    <col min="6" max="6" width="54.33203125" customWidth="1"/>
-    <col min="7" max="7" width="2" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.5" customWidth="1"/>
-    <col min="10" max="10" width="2.1640625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="48.1640625" customWidth="1"/>
+    <col min="4" max="4" width="29.83203125" customWidth="1"/>
+    <col min="5" max="5" width="58.83203125" customWidth="1"/>
+    <col min="6" max="6" width="75.6640625" customWidth="1"/>
+    <col min="7" max="7" width="54.33203125" customWidth="1"/>
+    <col min="8" max="8" width="2" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.5" customWidth="1"/>
+    <col min="11" max="11" width="2.1640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="48.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="H1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>19</v>
+      <c r="D3" t="s">
+        <v>46</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="H3" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J3" s="4"/>
+      <c r="L3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>21</v>
+      <c r="D4" t="s">
+        <v>46</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="H4" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C5">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="K8" s="4"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="4"/>
       <c r="I9" s="4"/>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="J9" s="4"/>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="G10" s="4"/>
       <c r="I10" s="4"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="4"/>
       <c r="I11" s="4"/>
-      <c r="K11" s="4"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="D12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="4"/>
       <c r="I12" s="4"/>
-      <c r="K12" s="4"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J12" s="4"/>
+      <c r="L12" s="4"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C14">
         <v>4</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14">
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="4"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C15">
         <v>5</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C15">
-        <v>6</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>29</v>
+      <c r="D15" t="s">
+        <v>45</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="H15" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="K15" s="4"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="K16" s="4"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D17" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="4"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="G17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="K17" s="4"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J17" s="4"/>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>34</v>
+      <c r="D18" t="s">
+        <v>45</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="K18" s="4"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J18" s="4"/>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="G19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="K19" s="4"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J19" s="4"/>
+      <c r="L19" s="4"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="K20" s="4"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="G21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="L21" s="4"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="K21" s="4"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C22">
-        <v>5</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="G22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="K22" s="4"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="K23" s="4"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="J23" s="4"/>
+      <c r="L23" s="4"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="G24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="K24" s="4"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J24" s="4"/>
+      <c r="L24" s="4"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>45</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="K25" s="4"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C26">
+      <c r="J25" s="4"/>
+      <c r="L25" s="4"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="L27" s="4"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="L28" s="4"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C29">
         <v>3</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C27">
+      <c r="E29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C30">
         <v>4</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="K27" s="4"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C28">
+      <c r="E30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="L30" s="4"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C31">
         <v>5</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C29">
+      <c r="E31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C32">
         <v>6</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="K29" s="4"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C30">
+      <c r="E32" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="L35" s="4"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C37">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D38" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D41" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>45</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C46">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C47">
+        <v>5</v>
+      </c>
+      <c r="D47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C48">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C49">
         <v>7</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="K30" s="4"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D31" s="4"/>
-      <c r="E31" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="K31" s="4"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="K32" s="4"/>
-    </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="K33" s="4"/>
-    </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="K34" s="4"/>
-    </row>
-    <row r="35" spans="4:11" x14ac:dyDescent="0.2">
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="K35" s="4"/>
-    </row>
-    <row r="1048576" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D1048576" s="3"/>
-      <c r="E1048576" s="3"/>
-      <c r="F1048576" s="3"/>
+      <c r="D49" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C50">
+        <v>8</v>
+      </c>
+      <c r="D50" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C51">
+        <v>9</v>
+      </c>
+      <c r="D51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C52">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E53" s="4"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1048557" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E1048557" s="3"/>
+      <c r="F1048557" s="3"/>
+      <c r="G1048557" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0AC314-0FE0-E144-BF8B-F2E27DEE96CE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>